--- a/tame_output/ON/bt/strategyON_20231013.xlsx
+++ b/tame_output/ON/bt/strategyON_20231013.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.8%</t>
+          <t>129.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1748"/>
+  <dimension ref="A1:G1749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41714,7 +41714,7 @@
         <v>45210</v>
       </c>
       <c r="B1748" t="n">
-        <v>2.803024533326522</v>
+        <v>2.803354337398473</v>
       </c>
       <c r="C1748" t="n">
         <v>2.939301794739787</v>
@@ -41730,6 +41730,29 @@
       </c>
       <c r="G1748" t="n">
         <v>4.235791171394435</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="2" t="n">
+        <v>45211</v>
+      </c>
+      <c r="B1749" t="n">
+        <v>2.801533654545558</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>2.941291882277773</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>1.558350250960214</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>3.564275558348112</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>2.158398564679093</v>
+      </c>
+      <c r="G1749" t="n">
+        <v>4.23633102108523</v>
       </c>
     </row>
   </sheetData>
